--- a/www/ig/fhir/mesures/ValueSet-method-glucose-vs.xlsx
+++ b/www/ig/fhir/mesures/ValueSet-method-glucose-vs.xlsx
@@ -31,7 +31,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>3.1.0</t>
+    <t>3.2.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-02T08:41:57+00:00</t>
+    <t>2026-02-18T13:49:04+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
